--- a/backend/data/orders.xlsx
+++ b/backend/data/orders.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H49"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1176,13 +1176,507 @@
       <c r="G30" t="str">
         <v>pending</v>
       </c>
-      <c r="H30" s="1">
+      <c r="H30">
         <v>46124.79774306713</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>RNFZ-20260630-5884</v>
+      </c>
+      <c r="B31" t="str">
+        <v>nizar tollsty</v>
+      </c>
+      <c r="C31" t="str">
+        <v>0699613920</v>
+      </c>
+      <c r="D31" t="str">
+        <v>sidi bernoussi</v>
+      </c>
+      <c r="E31" t="str">
+        <v>Sophisticated Grey Office Blazer | qty: 1 | price: 250 | image: https://i.pinimg.com/736x/9e/4b/3d/9e4b3d7f5168a155944ebc2e846f761f.jpg</v>
+      </c>
+      <c r="F31">
+        <v>250</v>
+      </c>
+      <c r="G31" t="str">
+        <v>pending</v>
+      </c>
+      <c r="H31">
+        <v>46203.80934121528</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>RNFZ-20260713-9354</v>
+      </c>
+      <c r="B32" t="str">
+        <v>nizar tollsty</v>
+      </c>
+      <c r="C32" t="str">
+        <v>0699613920</v>
+      </c>
+      <c r="D32" t="str">
+        <v>sidi bernoussi</v>
+      </c>
+      <c r="E32" t="str">
+        <v>Classic Black V-Neck Knit Sweater for Women | qty: 1 | price: 150 | image: https://i.pinimg.com/736x/4f/9e/c8/4f9ec80bb97954340bf85b97be5900bc.jpg</v>
+      </c>
+      <c r="F32">
+        <v>150</v>
+      </c>
+      <c r="G32" t="str">
+        <v>pending</v>
+      </c>
+      <c r="H32">
+        <v>46216.67832717593</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>RNFZ-20260713-6957</v>
+      </c>
+      <c r="B33" t="str">
+        <v>nizar tollsty</v>
+      </c>
+      <c r="C33" t="str">
+        <v>0699613920</v>
+      </c>
+      <c r="D33" t="str">
+        <v>sidi bernoussi</v>
+      </c>
+      <c r="E33" t="str">
+        <v>Classic Black V-Neck Knit Sweater for Women | qty: 1 | price: 150 | image: https://i.pinimg.com/736x/4f/9e/c8/4f9ec80bb97954340bf85b97be5900bc.jpg || Sophisticated Grey Office Blazer | qty: 1 | price: 250 | image: https://i.pinimg.com/736x/9e/4b/3d/9e4b3d7f5168a155944ebc2e846f761f.jpg</v>
+      </c>
+      <c r="F33">
+        <v>400</v>
+      </c>
+      <c r="G33" t="str">
+        <v>pending</v>
+      </c>
+      <c r="H33">
+        <v>46216.67875171296</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>RNFZ-20260713-1875</v>
+      </c>
+      <c r="B34" t="str">
+        <v>nizar tollsty</v>
+      </c>
+      <c r="C34" t="str">
+        <v>0699613920</v>
+      </c>
+      <c r="D34" t="str">
+        <v>sidi bernoussi</v>
+      </c>
+      <c r="E34" t="str">
+        <v>Classic Black V-Neck Knit Sweater for Women | qty: 1 | price: 150 | image: https://i.pinimg.com/736x/4f/9e/c8/4f9ec80bb97954340bf85b97be5900bc.jpg</v>
+      </c>
+      <c r="F34">
+        <v>150</v>
+      </c>
+      <c r="G34" t="str">
+        <v>pending</v>
+      </c>
+      <c r="H34">
+        <v>46216.67959054398</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>RNFZ-20260713-1638</v>
+      </c>
+      <c r="B35" t="str">
+        <v>nizar tollsty</v>
+      </c>
+      <c r="C35" t="str">
+        <v>0699613920</v>
+      </c>
+      <c r="D35" t="str">
+        <v>sidi bernoussi</v>
+      </c>
+      <c r="E35" t="str">
+        <v>Classic Black V-Neck Knit Sweater for Women | qty: 1 | price: 150 | image: https://i.pinimg.com/736x/4f/9e/c8/4f9ec80bb97954340bf85b97be5900bc.jpg</v>
+      </c>
+      <c r="F35">
+        <v>150</v>
+      </c>
+      <c r="G35" t="str">
+        <v>pending</v>
+      </c>
+      <c r="H35">
+        <v>46216.68745439815</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="str">
+        <v>RNFZ-20260713-8999</v>
+      </c>
+      <c r="B36" t="str">
+        <v>nizar tollsty</v>
+      </c>
+      <c r="C36" t="str">
+        <v>0699613920</v>
+      </c>
+      <c r="D36" t="str">
+        <v>sidi bernoussi</v>
+      </c>
+      <c r="E36" t="str">
+        <v>Classic Black V-Neck Knit Sweater for Women | qty: 1 | price: 150 | image: https://i.pinimg.com/736x/4f/9e/c8/4f9ec80bb97954340bf85b97be5900bc.jpg</v>
+      </c>
+      <c r="F36">
+        <v>150</v>
+      </c>
+      <c r="G36" t="str">
+        <v>pending</v>
+      </c>
+      <c r="H36">
+        <v>46216.68764440972</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="str">
+        <v>RNFZ-20260713-5217</v>
+      </c>
+      <c r="B37" t="str">
+        <v>nizar tollsty</v>
+      </c>
+      <c r="C37" t="str">
+        <v>0699613920</v>
+      </c>
+      <c r="D37" t="str">
+        <v>sidi bernoussi</v>
+      </c>
+      <c r="E37" t="str">
+        <v>Classic Black V-Neck Knit Sweater for Women | qty: 1 | price: 150 | image: https://i.pinimg.com/736x/4f/9e/c8/4f9ec80bb97954340bf85b97be5900bc.jpg</v>
+      </c>
+      <c r="F37">
+        <v>150</v>
+      </c>
+      <c r="G37" t="str">
+        <v>pending</v>
+      </c>
+      <c r="H37">
+        <v>46216.68920219907</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>RNFZ-20260713-7287</v>
+      </c>
+      <c r="B38" t="str">
+        <v>nizar tollsty</v>
+      </c>
+      <c r="C38" t="str">
+        <v>0699613920</v>
+      </c>
+      <c r="D38" t="str">
+        <v>sidi bernoussi</v>
+      </c>
+      <c r="E38" t="str">
+        <v>Classic Black V-Neck Knit Sweater for Women | qty: 1 | price: 150 | image: https://i.pinimg.com/736x/4f/9e/c8/4f9ec80bb97954340bf85b97be5900bc.jpg</v>
+      </c>
+      <c r="F38">
+        <v>150</v>
+      </c>
+      <c r="G38" t="str">
+        <v>pending</v>
+      </c>
+      <c r="H38">
+        <v>46216.691758912035</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>RNFZ-20260713-6531</v>
+      </c>
+      <c r="B39" t="str">
+        <v>nizar tollsty</v>
+      </c>
+      <c r="C39" t="str">
+        <v>0699613920</v>
+      </c>
+      <c r="D39" t="str">
+        <v>sidi bernoussi</v>
+      </c>
+      <c r="E39" t="str">
+        <v>Sophisticated Grey Office Blazer | qty: 1 | price: 250 | image: https://i.pinimg.com/736x/9e/4b/3d/9e4b3d7f5168a155944ebc2e846f761f.jpg</v>
+      </c>
+      <c r="F39">
+        <v>250</v>
+      </c>
+      <c r="G39" t="str">
+        <v>pending</v>
+      </c>
+      <c r="H39">
+        <v>46216.69464175926</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>RNFZ-20260713-9643</v>
+      </c>
+      <c r="B40" t="str">
+        <v>nizar tollsty</v>
+      </c>
+      <c r="C40" t="str">
+        <v>0699613920</v>
+      </c>
+      <c r="D40" t="str">
+        <v>sidi bernoussi</v>
+      </c>
+      <c r="E40" t="str">
+        <v>Classic Black V-Neck Knit Sweater for Women | qty: 1 | price: 150 | image: https://i.pinimg.com/736x/4f/9e/c8/4f9ec80bb97954340bf85b97be5900bc.jpg</v>
+      </c>
+      <c r="F40">
+        <v>150</v>
+      </c>
+      <c r="G40" t="str">
+        <v>pending</v>
+      </c>
+      <c r="H40">
+        <v>46216.69478923611</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>RNFZ-20260713-1456</v>
+      </c>
+      <c r="B41" t="str">
+        <v>nizar tollsty</v>
+      </c>
+      <c r="C41" t="str">
+        <v>0699613920</v>
+      </c>
+      <c r="D41" t="str">
+        <v>sidi bernoussi</v>
+      </c>
+      <c r="E41" t="str">
+        <v>Sophisticated Grey Office Blazer | qty: 1 | price: 250 | image: https://i.pinimg.com/736x/9e/4b/3d/9e4b3d7f5168a155944ebc2e846f761f.jpg</v>
+      </c>
+      <c r="F41">
+        <v>250</v>
+      </c>
+      <c r="G41" t="str">
+        <v>pending</v>
+      </c>
+      <c r="H41">
+        <v>46216.70275318287</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>RNFZ-20260713-5241</v>
+      </c>
+      <c r="B42" t="str">
+        <v>nizar tollsty</v>
+      </c>
+      <c r="C42" t="str">
+        <v>0699613920</v>
+      </c>
+      <c r="D42" t="str">
+        <v>sidi bernoussi</v>
+      </c>
+      <c r="E42" t="str">
+        <v>Elegant Modest White Maxi Dress with Puff Sleeves | qty: 1 | price: 650 | image: https://res.cloudinary.com/dhztkrs0s/image/upload/v1782680935/rihab_store/products/hnigmogqg6m88pheky91.jpg</v>
+      </c>
+      <c r="F42">
+        <v>650</v>
+      </c>
+      <c r="G42" t="str">
+        <v>pending</v>
+      </c>
+      <c r="H42">
+        <v>46216.72054288194</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="str">
+        <v>RNFZ-20260713-5772</v>
+      </c>
+      <c r="B43" t="str">
+        <v>nizar tollsty</v>
+      </c>
+      <c r="C43" t="str">
+        <v>0699613920</v>
+      </c>
+      <c r="D43" t="str">
+        <v>sidi bernoussi</v>
+      </c>
+      <c r="E43" t="str">
+        <v>Classic Black V-Neck Knit Sweater for Women | qty: 1 | price: 150 | image: https://i.pinimg.com/736x/4f/9e/c8/4f9ec80bb97954340bf85b97be5900bc.jpg</v>
+      </c>
+      <c r="F43">
+        <v>150</v>
+      </c>
+      <c r="G43" t="str">
+        <v>pending</v>
+      </c>
+      <c r="H43">
+        <v>46216.724994895834</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="str">
+        <v>RNFZ-20260713-4623</v>
+      </c>
+      <c r="B44" t="str">
+        <v>nizar tollsty</v>
+      </c>
+      <c r="C44" t="str">
+        <v>0699613920</v>
+      </c>
+      <c r="D44" t="str">
+        <v>sidi bernoussi</v>
+      </c>
+      <c r="E44" t="str">
+        <v>Elegant Modest White Maxi Dress with Puff Sleeves | qty: 1 | price: 650 | image: https://res.cloudinary.com/dhztkrs0s/image/upload/v1782680935/rihab_store/products/hnigmogqg6m88pheky91.jpg</v>
+      </c>
+      <c r="F44">
+        <v>650</v>
+      </c>
+      <c r="G44" t="str">
+        <v>pending</v>
+      </c>
+      <c r="H44">
+        <v>46216.72751369213</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="str">
+        <v>RNFZ-20260713-2399</v>
+      </c>
+      <c r="B45" t="str">
+        <v>thfgh</v>
+      </c>
+      <c r="C45" t="str">
+        <v>fghfgj</v>
+      </c>
+      <c r="D45" t="str">
+        <v>fgjfgjfgj</v>
+      </c>
+      <c r="E45" t="str">
+        <v>Sophisticated Grey Office Blazer | qty: 1 | price: 250 | image: https://i.pinimg.com/736x/9e/4b/3d/9e4b3d7f5168a155944ebc2e846f761f.jpg</v>
+      </c>
+      <c r="F45">
+        <v>250</v>
+      </c>
+      <c r="G45" t="str">
+        <v>pending</v>
+      </c>
+      <c r="H45">
+        <v>46216.729051539354</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="str">
+        <v>RNFZ-20260714-4830</v>
+      </c>
+      <c r="B46" t="str">
+        <v>nizar tollsty</v>
+      </c>
+      <c r="C46" t="str">
+        <v>0699613920</v>
+      </c>
+      <c r="D46" t="str">
+        <v>sidi bernoussi</v>
+      </c>
+      <c r="E46" t="str">
+        <v>Sophisticated Grey Office Blazer | qty: 1 | price: 250 | image: https://i.pinimg.com/736x/9e/4b/3d/9e4b3d7f5168a155944ebc2e846f761f.jpg</v>
+      </c>
+      <c r="F46">
+        <v>250</v>
+      </c>
+      <c r="G46" t="str">
+        <v>pending</v>
+      </c>
+      <c r="H46">
+        <v>46217.027451030095</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="str">
+        <v>RNFZ-20260714-3306</v>
+      </c>
+      <c r="B47" t="str">
+        <v>nizar tollsty</v>
+      </c>
+      <c r="C47" t="str">
+        <v>0699613920</v>
+      </c>
+      <c r="D47" t="str">
+        <v>sidi bernoussi</v>
+      </c>
+      <c r="E47" t="str">
+        <v>zzz | qty: 1 | price: 25665 | image: https://res.cloudinary.com/dhztkrs0s/image/upload/v1783986064/rihab_store/products/khg0qppcmizq77dutmsq.png</v>
+      </c>
+      <c r="F47">
+        <v>25665</v>
+      </c>
+      <c r="G47" t="str">
+        <v>pending</v>
+      </c>
+      <c r="H47">
+        <v>46217.028536736114</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="str">
+        <v>RNFZ-20260714-6279</v>
+      </c>
+      <c r="B48" t="str">
+        <v>nizar tollsty</v>
+      </c>
+      <c r="C48" t="str">
+        <v>0699613920</v>
+      </c>
+      <c r="D48" t="str">
+        <v>sidi bernoussi</v>
+      </c>
+      <c r="E48" t="str">
+        <v>zzz | qty: 1 | price: 25665 | image: https://res.cloudinary.com/dhztkrs0s/image/upload/v1783986064/rihab_store/products/khg0qppcmizq77dutmsq.png</v>
+      </c>
+      <c r="F48">
+        <v>25665</v>
+      </c>
+      <c r="G48" t="str">
+        <v>pending</v>
+      </c>
+      <c r="H48">
+        <v>46217.02923309028</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="str">
+        <v>RNFZ-20260714-7609</v>
+      </c>
+      <c r="B49" t="str">
+        <v>nizar tollsty</v>
+      </c>
+      <c r="C49" t="str">
+        <v>0699613920</v>
+      </c>
+      <c r="D49" t="str">
+        <v>sidi bernoussi</v>
+      </c>
+      <c r="E49" t="str">
+        <v>Sophisticated Grey Office Blazer | qty: 1 | price: 250 | image: https://i.pinimg.com/736x/9e/4b/3d/9e4b3d7f5168a155944ebc2e846f761f.jpg</v>
+      </c>
+      <c r="F49">
+        <v>250</v>
+      </c>
+      <c r="G49" t="str">
+        <v>pending</v>
+      </c>
+      <c r="H49" s="1">
+        <v>46217.03136699074</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H30"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H49"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/backend/data/orders.xlsx
+++ b/backend/data/orders.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H49"/>
+  <dimension ref="A1:H51"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1670,13 +1670,65 @@
       <c r="G49" t="str">
         <v>pending</v>
       </c>
-      <c r="H49" s="1">
+      <c r="H49">
         <v>46217.03136699074</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="str">
+        <v>RNFZ-20260714-3029</v>
+      </c>
+      <c r="B50" t="str">
+        <v>dfbfxbdfb</v>
+      </c>
+      <c r="C50" t="str">
+        <v>+212699613920</v>
+      </c>
+      <c r="D50" t="str">
+        <v>gnfgnfnfgnfgnfgnfgn</v>
+      </c>
+      <c r="E50" t="str">
+        <v>zzz | qty: 1 | price: 25665 | image: https://res.cloudinary.com/dhztkrs0s/image/upload/v1783986064/rihab_store/products/khg0qppcmizq77dutmsq.png</v>
+      </c>
+      <c r="F50">
+        <v>25665</v>
+      </c>
+      <c r="G50" t="str">
+        <v>pending</v>
+      </c>
+      <c r="H50">
+        <v>46217.15107673611</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="str">
+        <v>RNFZ-20260714-3227</v>
+      </c>
+      <c r="B51" t="str">
+        <v>fg,nbv,vb,v,</v>
+      </c>
+      <c r="C51" t="str">
+        <v>+212564651354</v>
+      </c>
+      <c r="D51" t="str">
+        <v>bvn,bnvc,v,b,</v>
+      </c>
+      <c r="E51" t="str">
+        <v>zzz | qty: 15 | price: 25665 | image: https://res.cloudinary.com/dhztkrs0s/image/upload/v1783986064/rihab_store/products/khg0qppcmizq77dutmsq.png</v>
+      </c>
+      <c r="F51">
+        <v>384975</v>
+      </c>
+      <c r="G51" t="str">
+        <v>pending</v>
+      </c>
+      <c r="H51" s="1">
+        <v>46217.15210446759</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H49"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H51"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/backend/data/orders.xlsx
+++ b/backend/data/orders.xlsx
@@ -398,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H51"/>
+  <dimension ref="A1:H53"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1722,13 +1722,65 @@
       <c r="G51" t="str">
         <v>pending</v>
       </c>
-      <c r="H51" s="1">
+      <c r="H51">
         <v>46217.15210446759</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="str">
+        <v>RNFZ-20260716-2111</v>
+      </c>
+      <c r="B52" t="str">
+        <v>rinifaza</v>
+      </c>
+      <c r="C52" t="str">
+        <v>+212605238023</v>
+      </c>
+      <c r="D52" t="str">
+        <v>dadada</v>
+      </c>
+      <c r="E52" t="str">
+        <v>Elegant Modest White Maxi Dress with Puff Sleeves | qty: 1 | price: 650 | image: https://res.cloudinary.com/dhztkrs0s/image/upload/v1782680935/rihab_store/products/hnigmogqg6m88pheky91.jpg</v>
+      </c>
+      <c r="F52">
+        <v>650</v>
+      </c>
+      <c r="G52" t="str">
+        <v>pending</v>
+      </c>
+      <c r="H52">
+        <v>46219.053475347224</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="str">
+        <v>RNFZ-20260716-4245</v>
+      </c>
+      <c r="B53" t="str">
+        <v>zack</v>
+      </c>
+      <c r="C53" t="str">
+        <v>+212605238023</v>
+      </c>
+      <c r="D53" t="str">
+        <v>casa</v>
+      </c>
+      <c r="E53" t="str">
+        <v>Elegant Modest White Maxi Dress with Puff Sleeves | qty: 1 | price: 650 | image: https://res.cloudinary.com/dhztkrs0s/image/upload/v1782680935/rihab_store/products/hnigmogqg6m88pheky91.jpg</v>
+      </c>
+      <c r="F53">
+        <v>650</v>
+      </c>
+      <c r="G53" t="str">
+        <v>pending</v>
+      </c>
+      <c r="H53" s="1">
+        <v>46219.06710074074</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H51"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H53"/>
   </ignoredErrors>
 </worksheet>
 </file>